--- a/2026 교육과정 박람회 2학년 타임별 부스 배치.xlsx
+++ b/2026 교육과정 박람회 2학년 타임별 부스 배치.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\2026 교육과정부\1. 고교학점제\교육과정 박람회\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://knue365-my.sharepoint.com/personal/20217346_ofc_knue_ac_kr/Documents/Claude Code/schs_curriculum_fair/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{944E7085-B0B4-4698-B2A0-BF371D5BEB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73057EBF-FAE8-41EA-8C7A-C95C3738B7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83C7F97-D780-4390-A559-3EE2CD6C15D5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C3643AD8-6030-4077-B6F4-E4F152EEA788}"/>
   </bookViews>
   <sheets>
-    <sheet name="이동반편성 내역(교육과정 박람회)" sheetId="1" r:id="rId1"/>
+    <sheet name="이동반편성 내역(선택과목 박람회)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,9 +39,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
-  <si>
-    <t>이동반편성 내역(교육과정 박람회)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+  <si>
+    <t>이동반편성 내역(선택과목 박람회)</t>
   </si>
   <si>
     <t>순번</t>
@@ -110,6 +110,9 @@
     <t>법과 사회</t>
   </si>
   <si>
+    <t>도시의 미래 탐구</t>
+  </si>
+  <si>
     <t>국제 관계의 이해</t>
   </si>
   <si>
@@ -117,15 +120,6 @@
   </si>
   <si>
     <t>금융과 경제생활</t>
-  </si>
-  <si>
-    <t>인간과 경제활동</t>
-  </si>
-  <si>
-    <t>인간과 심리</t>
-  </si>
-  <si>
-    <t>교육의 이해</t>
   </si>
   <si>
     <t>행성 우주과학</t>
@@ -538,8 +532,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97D7CE54-7E49-488C-9189-BEFB2EB5A2AE}">
-  <dimension ref="A1:L30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C386D73-AA2A-490F-BFCD-1C144757159D}">
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -590,28 +584,28 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E3">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F3">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G3">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="H3">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="I3">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J3">
-        <v>1129</v>
+        <v>1206</v>
       </c>
       <c r="K3">
-        <v>1129</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -631,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -648,28 +642,31 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
       </c>
       <c r="F5">
+        <v>26</v>
+      </c>
+      <c r="G5">
+        <v>24</v>
+      </c>
+      <c r="H5">
+        <v>26</v>
+      </c>
+      <c r="I5">
         <v>27</v>
       </c>
-      <c r="G5">
-        <v>28</v>
-      </c>
-      <c r="H5">
-        <v>28</v>
-      </c>
-      <c r="I5">
-        <v>28</v>
-      </c>
       <c r="J5">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="K5">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
@@ -680,19 +677,19 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>25</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
       </c>
       <c r="J6">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K6">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -706,19 +703,19 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="H7">
-        <v>18</v>
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="K7">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L7">
         <v>2</v>
@@ -732,25 +729,28 @@
         <v>16</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>25</v>
-      </c>
-      <c r="F8">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>19</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="K8">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -761,16 +761,16 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>21</v>
-      </c>
-      <c r="H9">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K9">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -784,19 +784,19 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10">
-        <v>17</v>
-      </c>
-      <c r="F10">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="I10">
+        <v>16</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L10">
         <v>2</v>
@@ -810,16 +810,16 @@
         <v>19</v>
       </c>
       <c r="C11">
-        <v>14</v>
-      </c>
-      <c r="G11">
-        <v>14</v>
+        <v>21</v>
+      </c>
+      <c r="D11">
+        <v>21</v>
       </c>
       <c r="J11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K11">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -836,22 +836,25 @@
         <v>21</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="F12">
+        <v>22</v>
       </c>
       <c r="G12">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J12">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="K12">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -862,19 +865,22 @@
         <v>21</v>
       </c>
       <c r="C13">
-        <v>28</v>
-      </c>
-      <c r="I13">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="F13">
+        <v>17</v>
+      </c>
+      <c r="H13">
+        <v>16</v>
       </c>
       <c r="J13">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K13">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -885,19 +891,19 @@
         <v>22</v>
       </c>
       <c r="C14">
-        <v>24</v>
-      </c>
-      <c r="E14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G14">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="I14">
+        <v>27</v>
       </c>
       <c r="J14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L14">
         <v>2</v>
@@ -913,10 +919,10 @@
       <c r="C15">
         <v>20</v>
       </c>
-      <c r="E15">
+      <c r="H15">
         <v>20</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>20</v>
       </c>
       <c r="J15">
@@ -937,25 +943,22 @@
         <v>24</v>
       </c>
       <c r="C16">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16">
-        <v>20</v>
-      </c>
-      <c r="F16">
-        <v>21</v>
-      </c>
-      <c r="G16">
+        <v>22</v>
+      </c>
+      <c r="H16">
         <v>21</v>
       </c>
       <c r="J16">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="K16">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
@@ -966,22 +969,25 @@
         <v>25</v>
       </c>
       <c r="C17">
-        <v>25</v>
-      </c>
-      <c r="G17">
-        <v>25</v>
-      </c>
-      <c r="I17">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="E17">
+        <v>23</v>
+      </c>
+      <c r="F17">
+        <v>23</v>
+      </c>
+      <c r="H17">
+        <v>21</v>
       </c>
       <c r="J17">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="K17">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
@@ -992,19 +998,19 @@
         <v>26</v>
       </c>
       <c r="C18">
-        <v>16</v>
-      </c>
-      <c r="D18">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="F18">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>25</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="K18">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="L18">
         <v>2</v>
@@ -1018,25 +1024,19 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>22</v>
-      </c>
-      <c r="F19">
-        <v>20</v>
-      </c>
-      <c r="H19">
-        <v>22</v>
-      </c>
-      <c r="I19">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
       </c>
       <c r="J19">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="K19">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="L19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1049,17 +1049,20 @@
       <c r="C20">
         <v>26</v>
       </c>
-      <c r="F20">
+      <c r="G20">
+        <v>25</v>
+      </c>
+      <c r="H20">
         <v>26</v>
       </c>
       <c r="J20">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="K20">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1070,19 +1073,25 @@
         <v>29</v>
       </c>
       <c r="C21">
-        <v>15</v>
-      </c>
-      <c r="G21">
-        <v>15</v>
+        <v>19</v>
+      </c>
+      <c r="E21">
+        <v>17</v>
+      </c>
+      <c r="F21">
+        <v>19</v>
+      </c>
+      <c r="I21">
+        <v>19</v>
       </c>
       <c r="J21">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="K21">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
@@ -1093,19 +1102,19 @@
         <v>30</v>
       </c>
       <c r="C22">
-        <v>24</v>
-      </c>
-      <c r="F22">
         <v>23</v>
       </c>
       <c r="G22">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="H22">
+        <v>23</v>
       </c>
       <c r="J22">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L22">
         <v>2</v>
@@ -1119,22 +1128,19 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>28</v>
-      </c>
-      <c r="D23">
-        <v>28</v>
-      </c>
-      <c r="I23">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="F23">
+        <v>21</v>
       </c>
       <c r="J23">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="K23">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -1147,20 +1153,23 @@
       <c r="C24">
         <v>19</v>
       </c>
-      <c r="F24">
+      <c r="E24">
         <v>19</v>
       </c>
-      <c r="H24">
+      <c r="G24">
+        <v>17</v>
+      </c>
+      <c r="I24">
         <v>19</v>
       </c>
       <c r="J24">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="K24">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -1171,19 +1180,22 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>18</v>
-      </c>
-      <c r="D25">
-        <v>18</v>
+        <v>27</v>
+      </c>
+      <c r="E25">
+        <v>27</v>
+      </c>
+      <c r="F25">
+        <v>27</v>
       </c>
       <c r="J25">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="K25">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
@@ -1194,19 +1206,19 @@
         <v>34</v>
       </c>
       <c r="C26">
+        <v>25</v>
+      </c>
+      <c r="D26">
         <v>26</v>
       </c>
-      <c r="E26">
-        <v>26</v>
-      </c>
       <c r="I26">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J26">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K26">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L26">
         <v>2</v>
@@ -1222,17 +1234,17 @@
       <c r="C27">
         <v>24</v>
       </c>
-      <c r="H27">
-        <v>24</v>
+      <c r="E27">
+        <v>23</v>
       </c>
       <c r="I27">
         <v>24</v>
       </c>
       <c r="J27">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K27">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L27">
         <v>2</v>
@@ -1246,73 +1258,21 @@
         <v>36</v>
       </c>
       <c r="C28">
-        <v>21</v>
-      </c>
-      <c r="E28">
-        <v>21</v>
-      </c>
-      <c r="G28">
+        <v>23</v>
+      </c>
+      <c r="D28">
+        <v>24</v>
+      </c>
+      <c r="F28">
         <v>21</v>
       </c>
       <c r="J28">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K28">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29">
-        <v>19</v>
-      </c>
-      <c r="D29">
-        <v>19</v>
-      </c>
-      <c r="F29">
-        <v>19</v>
-      </c>
-      <c r="J29">
-        <v>38</v>
-      </c>
-      <c r="K29">
-        <v>38</v>
-      </c>
-      <c r="L29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30">
-        <v>18</v>
-      </c>
-      <c r="D30">
-        <v>18</v>
-      </c>
-      <c r="I30">
-        <v>18</v>
-      </c>
-      <c r="J30">
-        <v>36</v>
-      </c>
-      <c r="K30">
-        <v>36</v>
-      </c>
-      <c r="L30">
         <v>2</v>
       </c>
     </row>
